--- a/artfynd/A 32897-2023 artfynd.xlsx
+++ b/artfynd/A 32897-2023 artfynd.xlsx
@@ -1691,7 +1691,7 @@
         <v>113407082</v>
       </c>
       <c r="B11" t="n">
-        <v>79168</v>
+        <v>79184</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 32897-2023 artfynd.xlsx
+++ b/artfynd/A 32897-2023 artfynd.xlsx
@@ -1691,7 +1691,7 @@
         <v>113407082</v>
       </c>
       <c r="B11" t="n">
-        <v>79184</v>
+        <v>79196</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 32897-2023 artfynd.xlsx
+++ b/artfynd/A 32897-2023 artfynd.xlsx
@@ -1691,7 +1691,7 @@
         <v>113407082</v>
       </c>
       <c r="B11" t="n">
-        <v>79196</v>
+        <v>79218</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 32897-2023 artfynd.xlsx
+++ b/artfynd/A 32897-2023 artfynd.xlsx
@@ -1691,7 +1691,7 @@
         <v>113407082</v>
       </c>
       <c r="B11" t="n">
-        <v>79218</v>
+        <v>79222</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 32897-2023 artfynd.xlsx
+++ b/artfynd/A 32897-2023 artfynd.xlsx
@@ -1691,7 +1691,7 @@
         <v>113407082</v>
       </c>
       <c r="B11" t="n">
-        <v>79222</v>
+        <v>79228</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 32897-2023 artfynd.xlsx
+++ b/artfynd/A 32897-2023 artfynd.xlsx
@@ -1691,7 +1691,7 @@
         <v>113407082</v>
       </c>
       <c r="B11" t="n">
-        <v>79228</v>
+        <v>79235</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 32897-2023 artfynd.xlsx
+++ b/artfynd/A 32897-2023 artfynd.xlsx
@@ -1691,7 +1691,7 @@
         <v>113407082</v>
       </c>
       <c r="B11" t="n">
-        <v>79235</v>
+        <v>79237</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 32897-2023 artfynd.xlsx
+++ b/artfynd/A 32897-2023 artfynd.xlsx
@@ -1691,7 +1691,7 @@
         <v>113407082</v>
       </c>
       <c r="B11" t="n">
-        <v>79237</v>
+        <v>79265</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 32897-2023 artfynd.xlsx
+++ b/artfynd/A 32897-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1792,6 +1792,227 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>114666744</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57248</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Rogstabodsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>492860</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6940140</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-02-13</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-02-13</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>114666742</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57232</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Rogstabodsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>492894</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6940011</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-02-13</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-02-13</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32897-2023 artfynd.xlsx
+++ b/artfynd/A 32897-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 32897-2023 artfynd.xlsx
+++ b/artfynd/A 32897-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2013,6 +2013,327 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>114884886</v>
+      </c>
+      <c r="B14" t="n">
+        <v>97535</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Rogstabodsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>492793</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6940325</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2023-08-13</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2023-08-13</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>114884881</v>
+      </c>
+      <c r="B15" t="n">
+        <v>97535</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Rogstabodsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>492770</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6940321</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-08-13</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-08-13</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>114884869</v>
+      </c>
+      <c r="B16" t="n">
+        <v>97535</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Rogstabodsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>492733</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6940333</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2023-08-13</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2023-08-13</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32897-2023 artfynd.xlsx
+++ b/artfynd/A 32897-2023 artfynd.xlsx
@@ -4193,7 +4193,7 @@
         <v>119869852</v>
       </c>
       <c r="B34" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>

--- a/artfynd/A 32897-2023 artfynd.xlsx
+++ b/artfynd/A 32897-2023 artfynd.xlsx
@@ -4413,11 +4413,11 @@
         <v>120666231</v>
       </c>
       <c r="B36" t="n">
-        <v>91119</v>
+        <v>91168</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">

--- a/artfynd/A 32897-2023 artfynd.xlsx
+++ b/artfynd/A 32897-2023 artfynd.xlsx
@@ -1797,7 +1797,7 @@
         <v>114666742</v>
       </c>
       <c r="B12" t="n">
-        <v>57265</v>
+        <v>57478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>119405328</v>
       </c>
       <c r="B22" t="n">
-        <v>57310</v>
+        <v>57478</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>119405365</v>
       </c>
       <c r="B24" t="n">
-        <v>57310</v>
+        <v>57478</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>119869852</v>
       </c>
       <c r="B34" t="n">
-        <v>57320</v>
+        <v>57478</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>

--- a/artfynd/A 32897-2023 artfynd.xlsx
+++ b/artfynd/A 32897-2023 artfynd.xlsx
@@ -1797,7 +1797,7 @@
         <v>114666742</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>119405328</v>
       </c>
       <c r="B22" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>119405365</v>
       </c>
       <c r="B24" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>119869852</v>
       </c>
       <c r="B34" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>

--- a/artfynd/A 32897-2023 artfynd.xlsx
+++ b/artfynd/A 32897-2023 artfynd.xlsx
@@ -1797,7 +1797,7 @@
         <v>114666742</v>
       </c>
       <c r="B12" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>119405328</v>
       </c>
       <c r="B22" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>119405365</v>
       </c>
       <c r="B24" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>119869852</v>
       </c>
       <c r="B34" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>

--- a/artfynd/A 32897-2023 artfynd.xlsx
+++ b/artfynd/A 32897-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY48"/>
+  <dimension ref="A1:AZ48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110377105</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111326485</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -979,6 +994,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112983587</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1087,6 +1107,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112983066</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1188,6 +1213,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120666252</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1289,6 +1319,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112987020</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1390,6 +1425,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120666231</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1498,6 +1538,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112983295</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1599,6 +1644,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119405306</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1700,6 +1750,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119417995</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1808,6 +1863,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112982997</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1916,6 +1976,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112983172</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2024,6 +2089,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112983439</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2132,6 +2202,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112983473</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2233,6 +2308,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119405314</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2334,6 +2414,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119405333</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2435,6 +2520,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119405357</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2543,6 +2633,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112982957</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2651,6 +2746,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112983153</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2759,6 +2859,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112983190</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2867,6 +2972,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112983546</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2968,6 +3078,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112987053</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3069,6 +3184,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112987076</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3170,6 +3290,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113407082</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3271,6 +3396,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119405311</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3372,6 +3502,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119417993</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3473,6 +3608,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119405299</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3574,6 +3714,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119417999</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3683,6 +3828,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114666744</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3785,6 +3935,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114666742</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3894,6 +4049,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119405328</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4003,6 +4163,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119405365</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4112,6 +4277,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119869852</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4217,6 +4387,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119405304</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4318,6 +4493,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119418066</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4427,6 +4607,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119405361</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4536,6 +4721,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119405364</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4638,6 +4828,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119417997</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4740,6 +4935,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114884869</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4842,6 +5042,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114884881</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4944,6 +5149,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114884886</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5054,6 +5264,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119405348</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5164,6 +5379,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119405353</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5266,6 +5486,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119418033</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5367,6 +5592,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119418055</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5468,6 +5698,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119418068</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5569,8 +5804,62 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119418058</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>